--- a/astro-site/public/dl/guia-restaurante-japones/cronograma-apertura-gantt.xlsx
+++ b/astro-site/public/dl/guia-restaurante-japones/cronograma-apertura-gantt.xlsx
@@ -10,7 +10,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instrucciones" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gantt" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'Gantt'!$4:$4</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -504,9 +506,9 @@
   <sheetPr>
     <tabColor rgb="00FFD700"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:C11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="80" customWidth="1" min="1" max="1"/>
@@ -526,6 +528,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -554,10 +557,19 @@
         </is>
       </c>
     </row>
+    <row r="8"/>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
           <t>Celdas verdes = campos editables</t>
+        </is>
+      </c>
+    </row>
+    <row r="10"/>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>Versión 1.1 · agosto 2026 · aichef.pro/guia-restaurante-japones · info@aichef.pro</t>
         </is>
       </c>
     </row>
@@ -566,7 +578,16 @@
     <mergeCell ref="A2:C2"/>
     <mergeCell ref="A1:C1"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -575,7 +596,7 @@
   <sheetPr>
     <tabColor rgb="00795548"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:O34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -611,6 +632,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
@@ -1418,6 +1440,7 @@
         </is>
       </c>
     </row>
+    <row r="33"/>
     <row r="34">
       <c r="A34" s="10" t="inlineStr">
         <is>
@@ -1431,6 +1454,15 @@
     <mergeCell ref="A1:O1"/>
     <mergeCell ref="A2:O2"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>